--- a/ig/DM-MARS-2026/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
+++ b/ig/DM-MARS-2026/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-03-30T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -466,7 +466,7 @@
     <t>259</t>
   </si>
   <si>
-    <t>Activ.Club et Équipe de Prévention</t>
+    <t>Prévention spécialisée</t>
   </si>
   <si>
     <t>262</t>
